--- a/outputs/etf_trend_strategy/threshold_0.8/backtests/window_40/return_r2/post_rank_positive_return/rebalance_1d/next_day_vwap/next_day_vwap_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.8/backtests/window_40/return_r2/post_rank_positive_return/rebalance_1d/next_day_vwap/next_day_vwap_annual_metrics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="annual_metrics" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="annual_metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'annual_metrics'!$A$1:$H$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'annual_metrics'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -462,17 +462,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -524,25 +524,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>-0.1030154026035907</v>
+        <v>-0.1367328852931615</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.3124624718420859</v>
+        <v>0.199200485870112</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>-0.2848579972704116</v>
+        <v>-0.8089524316060307</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.3909821120279323</v>
+        <v>-1.066898109921596</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2874329718507144</v>
+        <v>0.2160363687544028</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>-0.4022077671792201</v>
+        <v>-0.7085950430617308</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>31.73555041328127</v>
+        <v>38.27741781622321</v>
       </c>
     </row>
     <row r="3">
@@ -552,25 +552,25 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.2464420507357704</v>
+        <v>-0.04755006352035207</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.2423364881124007</v>
+        <v>0.2866781486651703</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>-1.155433380697079</v>
+        <v>-0.08632112430715093</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-1.512054383058842</v>
+        <v>-0.1236891142672601</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.2938321543602797</v>
+        <v>0.1929275813329789</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.8685279364082219</v>
+        <v>-0.256394339932874</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>39.34588376045794</v>
+        <v>23.87789038874135</v>
       </c>
     </row>
     <row r="4">
@@ -580,25 +580,25 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.06089289785548224</v>
+        <v>-0.07363264575946227</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.2336019920508866</v>
+        <v>0.2287335535852025</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>-0.2276187228440955</v>
+        <v>-0.2989985658126129</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.328328555082453</v>
+        <v>-0.4075080671933314</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.2475180864375434</v>
+        <v>0.2919897193272839</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.2558510276188347</v>
+        <v>-0.262186696539397</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>38.69997036199734</v>
+        <v>46.86612479855332</v>
       </c>
     </row>
     <row r="5">
@@ -608,25 +608,25 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-0.01446287360440501</v>
+        <v>0.03128069652492416</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.2267827362596503</v>
+        <v>0.2906726079887821</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>-0.02014228768248257</v>
+        <v>0.2022789222196267</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>-0.02969553688436744</v>
+        <v>0.3121858523521664</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.1849620968753417</v>
+        <v>0.2621341393704972</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.08140041628907559</v>
+        <v>0.12434142329769</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>40.53467344462951</v>
+        <v>39.79498889437268</v>
       </c>
     </row>
     <row r="6">
@@ -636,29 +636,57 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.284023999594349</v>
+        <v>0.616701968756705</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.2693375666861191</v>
+        <v>0.3222482689380615</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.042955610664001</v>
+        <v>1.662735579349107</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.457192217967421</v>
+        <v>2.416527495642739</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1800622567208175</v>
+        <v>0.2025408242973143</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.643699660200097</v>
+        <v>3.188117772001191</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>49.71135550348699</v>
+        <v>40.80051823164089</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026年截至07-31</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0.3395551186718981</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.4002851886977206</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>1.486417827818237</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>2.281017665362445</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0.1593159526519891</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>4.387011242682761</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>39.9007762413426</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H6"/>
+  <autoFilter ref="A1:H7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>